--- a/HLJT_online_PsychoPy/Messages.xlsx
+++ b/HLJT_online_PsychoPy/Messages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/HLJT/HLJT_online_PsychoPy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/HLJT/HLJT_local_PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="484" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8F5AFCB-C3AB-402E-A42F-3CD62F569757}"/>
+  <xr:revisionPtr revIDLastSave="488" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE06363A-7D32-44E7-9626-66EA62F35395}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -252,16 +252,6 @@
     <t>DE</t>
   </si>
   <si>
-    <t>Willkommen zur Hand-Lateralitäts-Bewertungsaufgabe!
-Zweck der Aufgabe ist es, Ihre Fähigkeit zu messen, Lateralisierungen (rechts/links) von Handbildern zu beurteilen.
-Drücken Sie die LEERTASTE, um zu starten.</t>
-  </si>
-  <si>
-    <t>Dies ist das Ende des Experiments.
-Vielen Dank für Ihre Teilnahme!
-Warten Sie 3 Sekunden, bevor Sie das Experiment beenden.</t>
-  </si>
-  <si>
     <t>Drücken Sie die LEERTASTE, um fortzufahren</t>
   </si>
   <si>
@@ -281,11 +271,6 @@
 Eine Meldung unten wird Ihnen anzeigen, wann Sie weitermachen können.</t>
   </si>
   <si>
-    <t>Sie werden nun mit einem Hauptaufgabenblock beginnen.
-Ihre Leistung ist in diesem Block wichtig.
-Sie müssen so SCHNELL UND GENAU wie möglich antworten.</t>
-  </si>
-  <si>
     <t>Sie haben den Block abgeschlossen.
 Nehmen Sie sich ein paar Sekunden Zeit, bevor Sie fortfahren.
 Eine Meldung unten wird Ihnen anzeigen, wann Sie weitermachen können.</t>
@@ -357,9 +342,6 @@
     <t>Beidhändig</t>
   </si>
   <si>
-    <t>Rechte</t>
-  </si>
-  <si>
     <t>Ambidextre</t>
   </si>
   <si>
@@ -504,13 +486,95 @@
     <t>Has terminado el bloque de práctica.
 Tómate unos pocos segundos antes de continuar al siguiente bloque.
 Verás un mensaje más abajo indicando que ya puedes seguir.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Willkommen zur Hand-Lateralitäts-Bewertungsaufgabe!
+Zweck der Aufgabe ist es, Ihre Fähigkeit zu messen, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lateralität</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (rechts/links) von Handbildern zu beurteilen.
+Drücken Sie die LEERTASTE, um zu starten.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dies ist das Ende des Experiments.
+Vielen Dank für Ihre Teilnahme!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Das Experiment endet in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3 Sekunden</t>
+    </r>
+  </si>
+  <si>
+    <t>Sie werden nun mit einem Hauptaufgabenblock beginnen.
+Ihre Leistung ist in diesem Block wichtig.
+Sie müssen so SCHNELL UND KORREKT wie möglich antworten.</t>
+  </si>
+  <si>
+    <t>Rechts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,6 +604,13 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -604,6 +675,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -940,7 +1015,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -957,7 +1032,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -974,7 +1049,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -991,7 +1066,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1008,7 +1083,7 @@
         <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1025,7 +1100,7 @@
         <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1036,13 +1111,13 @@
         <v>32</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1059,7 +1134,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1076,245 +1151,245 @@
         <v>34</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="E21" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" t="s">
         <v>104</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
